--- a/output/pdf_financials_xlsx/NXS.xlsx
+++ b/output/pdf_financials_xlsx/NXS.xlsx
@@ -4754,43 +4754,43 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.517086</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.823272</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.958018</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.286823</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.432817</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.996922</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.577204</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.077078</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.200287</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.200287</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.223371</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.223371</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.230805</v>
       </c>
     </row>
     <row r="93">
@@ -5934,22 +5934,22 @@
         <v>-1.691729</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.895031</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.95672</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.17</v>
+        <v>-0.890564</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.1</v>
+        <v>-2.154922</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0.2</v>
+        <v>-0.112918</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.033068</v>
       </c>
       <c r="M118" s="3" t="n">
         <v>0</v>
@@ -7797,7 +7797,11 @@
           <t>Share-based payment reserve (note 7)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -8842,7 +8846,11 @@
           <t>Share-based payment reserve (note 10)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -9798,7 +9806,11 @@
           <t>Share-based payment reserve (note 11)</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -10274,7 +10286,11 @@
           <t>Share-based payment reserve (note 11)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -11913,7 +11929,11 @@
           <t>Share-based payment reserve (note 9)</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -12861,7 +12881,11 @@
           <t>Share-based payment reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -13653,7 +13677,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -15028,7 +15056,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -15350,7 +15382,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E109" s="5" t="n">
         <v>0.517086</v>
       </c>
@@ -17913,7 +17949,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NXS.xlsx
+++ b/output/pdf_financials_xlsx/NXS.xlsx
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.0008630000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1678,7 +1678,7 @@
         <v>-2.332084</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.760187</v>
+        <v>-3.76105</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-5.292348</v>
@@ -1770,7 +1770,7 @@
         <v>-2.332084</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.760187</v>
+        <v>-3.76105</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-5.292348</v>
@@ -1998,43 +1998,43 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.007401</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.673144</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.07091799999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.360916</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.053524</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.422546</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.191574</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.19667</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.139349</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.030115</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.007062</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.009957000000000001</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.523559</v>
       </c>
     </row>
     <row r="35">
@@ -2090,43 +2090,43 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.007401</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.673144</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.07091799999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.360916</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.053524</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.422546</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.191574</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.19667</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.139349</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.045</v>
+        <v>0.075115</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.04</v>
+        <v>0.047062</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.009957000000000001</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.523559</v>
       </c>
     </row>
     <row r="37">
@@ -2642,43 +2642,43 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.028518</v>
+        <v>0.021117</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.9511039999999999</v>
+        <v>0.27796</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.086728</v>
+        <v>0.01581</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.497577</v>
+        <v>0.136661</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.380892</v>
+        <v>0.327368</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.512367</v>
+        <v>0.089821</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.546935</v>
+        <v>0.355361</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>3.045969</v>
+        <v>0.849299</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.85184</v>
+        <v>0.712491</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.257786</v>
+        <v>0.227671</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.062214</v>
+        <v>0.055152</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.017943</v>
+        <v>0.007986</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.563092</v>
+        <v>0.039533</v>
       </c>
     </row>
     <row r="49">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
@@ -25946,7 +25946,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -28483,7 +28483,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -29502,7 +29502,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -32293,7 +32293,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">

--- a/output/pdf_financials_xlsx/NXS.xlsx
+++ b/output/pdf_financials_xlsx/NXS.xlsx
@@ -697,25 +697,25 @@
         <v>1.074959</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.618373</v>
+        <v>0.749248</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.992036</v>
+        <v>1.118036</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.850892</v>
+        <v>0.967092</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.656707</v>
+        <v>0.746707</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.462024</v>
+        <v>0.524524</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>0.201988</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.306801</v>
+        <v>0.439301</v>
       </c>
     </row>
     <row r="8">
@@ -835,25 +835,25 @@
         <v>1.320319</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.261567</v>
+        <v>1.392442</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.833572</v>
+        <v>1.959572</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.340198</v>
+        <v>1.456398</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.98349</v>
+        <v>1.07349</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.462024</v>
+        <v>0.524524</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>0.209408</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.359193</v>
+        <v>0.491693</v>
       </c>
     </row>
     <row r="11">
@@ -881,25 +881,25 @@
         <v>-1.320319</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-1.261567</v>
+        <v>-1.392442</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-1.833572</v>
+        <v>-1.959572</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-1.340198</v>
+        <v>-1.456398</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.98349</v>
+        <v>-1.07349</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.462024</v>
+        <v>-0.524524</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>-0.209408</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.359193</v>
+        <v>-0.491693</v>
       </c>
     </row>
     <row r="12">
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.098692</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.377421</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>0</v>
@@ -3444,19 +3444,19 @@
         <v>0</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.225365</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.388834</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.562491</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.546078</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.104126</v>
       </c>
     </row>
     <row r="65">
@@ -3558,43 +3558,43 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.06265</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0408</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.030658</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.0355</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.05027</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.0567</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.046875</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.055</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.037901</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.038308</v>
       </c>
     </row>
     <row r="68">
@@ -5814,7 +5814,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.067278</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
@@ -17074,7 +17074,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -26019,7 +26023,11 @@
           <t>Management and directors’ fees (note 8)</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -28560,7 +28568,11 @@
           <t>Management and directors’ fees (note 11)</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -29654,7 +29666,11 @@
           <t>Management and directors’ fees (note 12)</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -31248,7 +31264,11 @@
           <t>Management and directors’ fees (note 10)</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
